--- a/samples/수주취합/고객사B_발주서.xlsx
+++ b/samples/수주취합/고객사B_발주서.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
   <si>
     <t>No</t>
   </si>
@@ -929,8 +929,8 @@
       <c r="AO2" t="s">
         <v>70</v>
       </c>
-      <c r="AP2" t="s">
-        <v>57</v>
+      <c r="AP2">
+        <v>42000</v>
       </c>
       <c r="AQ2" t="s">
         <v>57</v>
